--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251215_201306.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251215_201306.xlsx
@@ -5472,7 +5472,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251215_201306.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251215_201306.xlsx
@@ -5472,7 +5472,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
